--- a/Excel/RoleDialogDatas.xlsx
+++ b/Excel/RoleDialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12780"/>
+    <workbookView windowHeight="14880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
   <si>
     <t>int</t>
   </si>
@@ -198,6 +198,15 @@
   </si>
   <si>
     <t>迈克兽性大发，吃掉了朋友，游戏结束</t>
+  </si>
+  <si>
+    <t>一些上帝引导,这是玩家不触发bob敲门不让他出门的引导</t>
+  </si>
+  <si>
+    <t>一些上帝引导,这是让玩家和Bob在院子中进行探索的引导</t>
+  </si>
+  <si>
+    <t>一些上帝引导,这是第二天让玩家和Bob在院子中进行探索的引导</t>
   </si>
 </sst>
 </file>
@@ -210,7 +219,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +256,12 @@
     <font>
       <sz val="24"/>
       <color rgb="FF4472C4"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="4"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -715,137 +730,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -864,11 +879,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1396,16 +1414,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="9.22222222222222" defaultRowHeight="30.6"/>
+  <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
   <cols>
-    <col min="1" max="1" width="19.5555555555556" style="2" customWidth="1"/>
-    <col min="2" max="2" width="58.9814814814815" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.4444444444444" style="2" customWidth="1"/>
-    <col min="4" max="4" width="39.5555555555556" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.7777777777778" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.5576923076923" style="2" customWidth="1"/>
+    <col min="2" max="2" width="58.9807692307692" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.4423076923077" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.5576923076923" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.7788461538462" style="2" customWidth="1"/>
     <col min="6" max="6" width="35.25" style="2" customWidth="1"/>
-    <col min="7" max="9" width="27.5555555555556" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.22222222222222" style="2"/>
+    <col min="7" max="9" width="27.5576923076923" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.22115384615385" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1669,7 +1687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A10" s="5">
         <v>10007</v>
       </c>
@@ -1688,17 +1706,17 @@
       <c r="F10" s="5">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="60" spans="1:9">
+      <c r="H10" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A11" s="5">
         <v>10008</v>
       </c>
@@ -1717,17 +1735,17 @@
       <c r="F11" s="5">
         <v>0</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="60" spans="1:9">
+      <c r="H11" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A12" s="5">
         <v>10009</v>
       </c>
@@ -1746,17 +1764,17 @@
       <c r="F12" s="5">
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="60" spans="1:9">
+      <c r="H12" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A13" s="5">
         <v>10010</v>
       </c>
@@ -1775,17 +1793,17 @@
       <c r="F13" s="5">
         <v>0</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="60" spans="1:9">
+      <c r="H13" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A14" s="5">
         <v>10011</v>
       </c>
@@ -1804,21 +1822,21 @@
       <c r="F14" s="5">
         <v>0</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="60" spans="1:9">
+      <c r="H14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="69" spans="1:9">
       <c r="A15" s="4">
         <v>10012</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>2</v>
       </c>
       <c r="C15" s="4">
@@ -1843,7 +1861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="90" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="104" spans="1:9">
       <c r="A16" s="5">
         <v>10013</v>
       </c>
@@ -1862,17 +1880,17 @@
       <c r="F16" s="5">
         <v>0</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="90" spans="1:9">
+      <c r="H16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="104" spans="1:9">
       <c r="A17" s="4">
         <v>10014</v>
       </c>
@@ -1901,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="90" spans="1:9">
+    <row r="18" ht="104" spans="1:9">
       <c r="A18" s="4">
         <v>10015</v>
       </c>
@@ -1930,7 +1948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="90" spans="1:9">
+    <row r="19" ht="104" spans="1:9">
       <c r="A19" s="4">
         <v>10016</v>
       </c>
@@ -1959,7 +1977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="90" spans="1:9">
+    <row r="20" ht="104" spans="1:9">
       <c r="A20" s="4">
         <v>10017</v>
       </c>
@@ -1988,7 +2006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="90" spans="1:9">
+    <row r="21" ht="104" spans="1:9">
       <c r="A21" s="4">
         <v>10018</v>
       </c>
@@ -2017,7 +2035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="150" spans="1:9">
+    <row r="22" ht="172" spans="1:9">
       <c r="A22" s="4">
         <v>10019</v>
       </c>
@@ -2046,7 +2064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="120" spans="1:9">
+    <row r="23" ht="138" spans="1:9">
       <c r="A23" s="4">
         <v>10020</v>
       </c>
@@ -2075,7 +2093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="120" spans="1:9">
+    <row r="24" ht="138" spans="1:9">
       <c r="A24" s="4">
         <v>10021</v>
       </c>
@@ -2104,7 +2122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="25" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A25" s="5">
         <v>10022</v>
       </c>
@@ -2123,17 +2141,17 @@
       <c r="F25" s="5">
         <v>0</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H25" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="120" spans="1:9">
+      <c r="H25" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="138" spans="1:9">
       <c r="A26" s="4">
         <v>10023</v>
       </c>
@@ -2162,7 +2180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="210" spans="1:9">
+    <row r="27" ht="241" spans="1:9">
       <c r="A27" s="4">
         <v>10024</v>
       </c>
@@ -2191,7 +2209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="28" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A28" s="5">
         <v>10025</v>
       </c>
@@ -2210,17 +2228,17 @@
       <c r="F28" s="5">
         <v>0</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H28" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="60" spans="1:9">
+      <c r="H28" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A29" s="5">
         <v>10026</v>
       </c>
@@ -2239,17 +2257,17 @@
       <c r="F29" s="5">
         <v>0</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H29" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="60" spans="1:9">
+      <c r="H29" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A30" s="5">
         <v>10027</v>
       </c>
@@ -2268,22 +2286,22 @@
       <c r="F30" s="5">
         <v>0</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="H30" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="60" spans="1:9">
+      <c r="H30" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A31" s="5">
         <v>10028</v>
       </c>
       <c r="B31" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C31" s="5">
         <v>2301</v>
@@ -2291,23 +2309,23 @@
       <c r="D31" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="E31" s="5">
-        <v>-1</v>
+      <c r="E31" s="4">
+        <v>10024</v>
       </c>
       <c r="F31" s="5">
         <v>0</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="90" spans="1:9">
+      <c r="H31" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="104" spans="1:9">
       <c r="A32" s="4">
         <v>10029</v>
       </c>
@@ -2320,8 +2338,8 @@
       <c r="D32" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="E32" s="4">
-        <v>-1</v>
+      <c r="E32" s="5">
+        <v>10028</v>
       </c>
       <c r="F32" s="4">
         <v>1</v>
@@ -2333,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="I32" s="3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="120" spans="1:9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="138" spans="1:9">
       <c r="A33" s="4">
         <v>10030</v>
       </c>
@@ -2365,7 +2383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="120" spans="1:9">
+    <row r="34" ht="138" spans="1:9">
       <c r="A34" s="4">
         <v>10031</v>
       </c>
@@ -2394,7 +2412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="60" spans="1:9">
+    <row r="35" ht="69" spans="1:9">
       <c r="A35" s="4">
         <v>10032</v>
       </c>
@@ -2423,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="60" spans="1:9">
+    <row r="36" ht="69" spans="1:9">
       <c r="A36" s="4">
         <v>10033</v>
       </c>
@@ -2452,7 +2470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="60" spans="1:9">
+    <row r="37" ht="69" spans="1:9">
       <c r="A37" s="4">
         <v>10034</v>
       </c>
@@ -2481,7 +2499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" ht="60" spans="1:9">
+    <row r="38" ht="69" spans="1:9">
       <c r="A38" s="4">
         <v>10035</v>
       </c>
@@ -2510,7 +2528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="120" spans="1:9">
+    <row r="39" ht="138" spans="1:9">
       <c r="A39" s="4">
         <v>10036</v>
       </c>
@@ -2539,26 +2557,92 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
+    <row r="40" ht="172" spans="1:9">
+      <c r="A40" s="4">
+        <v>10037</v>
+      </c>
+      <c r="B40" s="4">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4">
+        <v>10050</v>
+      </c>
+      <c r="D40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H40" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="172" spans="1:9">
+      <c r="A41" s="4">
+        <v>10038</v>
+      </c>
+      <c r="B41" s="4">
+        <v>0</v>
+      </c>
+      <c r="C41" s="7">
+        <v>10550</v>
+      </c>
+      <c r="D41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F41" s="4">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="207" spans="1:9">
+      <c r="A42" s="4">
+        <v>10039</v>
+      </c>
+      <c r="B42" s="4">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4">
+        <v>11150</v>
+      </c>
+      <c r="D42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>10021</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4"/>

--- a/Excel/RoleDialogDatas.xlsx
+++ b/Excel/RoleDialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="14880"/>
+    <workbookView windowWidth="21000" windowHeight="12780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
   <si>
     <t>int</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>一些上帝引导,这是第二天让玩家和Bob在院子中进行探索的引导</t>
+  </si>
+  <si>
+    <t>一些上帝引导,这是第二天让玩家和Bob在客厅里喝牛奶，不要让玩家到卧室去的引导</t>
+  </si>
+  <si>
+    <t>一些上帝引导,这是第二天让玩家和Bob在客厅里喝牛奶，不要让玩家到院子去的引导</t>
   </si>
 </sst>
 </file>
@@ -879,14 +885,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1414,16 +1420,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
+  <sheetFormatPr defaultColWidth="9.22222222222222" defaultRowHeight="30.6"/>
   <cols>
-    <col min="1" max="1" width="19.5576923076923" style="2" customWidth="1"/>
-    <col min="2" max="2" width="58.9807692307692" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.4423076923077" style="2" customWidth="1"/>
-    <col min="4" max="4" width="39.5576923076923" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.7788461538462" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.5555555555556" style="2" customWidth="1"/>
+    <col min="2" max="2" width="58.9814814814815" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.4444444444444" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.5555555555556" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.7777777777778" style="2" customWidth="1"/>
     <col min="6" max="6" width="35.25" style="2" customWidth="1"/>
-    <col min="7" max="9" width="27.5576923076923" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.22115384615385" style="2"/>
+    <col min="7" max="9" width="27.5555555555556" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.22222222222222" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1687,7 +1693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="69" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A10" s="5">
         <v>10007</v>
       </c>
@@ -1706,17 +1712,17 @@
       <c r="F10" s="5">
         <v>0</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="69" spans="1:9">
+      <c r="H10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A11" s="5">
         <v>10008</v>
       </c>
@@ -1735,17 +1741,17 @@
       <c r="F11" s="5">
         <v>0</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="69" spans="1:9">
+      <c r="H11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A12" s="5">
         <v>10009</v>
       </c>
@@ -1764,17 +1770,17 @@
       <c r="F12" s="5">
         <v>0</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="69" spans="1:9">
+      <c r="H12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A13" s="5">
         <v>10010</v>
       </c>
@@ -1793,17 +1799,17 @@
       <c r="F13" s="5">
         <v>0</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="69" spans="1:9">
+      <c r="H13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A14" s="5">
         <v>10011</v>
       </c>
@@ -1822,21 +1828,21 @@
       <c r="F14" s="5">
         <v>0</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="69" spans="1:9">
+      <c r="H14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="60" spans="1:9">
       <c r="A15" s="4">
         <v>10012</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>2</v>
       </c>
       <c r="C15" s="4">
@@ -1861,7 +1867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="104" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="90" spans="1:9">
       <c r="A16" s="5">
         <v>10013</v>
       </c>
@@ -1880,17 +1886,17 @@
       <c r="F16" s="5">
         <v>0</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="104" spans="1:9">
+      <c r="H16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="90" spans="1:9">
       <c r="A17" s="4">
         <v>10014</v>
       </c>
@@ -1919,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="104" spans="1:9">
+    <row r="18" ht="90" spans="1:9">
       <c r="A18" s="4">
         <v>10015</v>
       </c>
@@ -1948,7 +1954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="104" spans="1:9">
+    <row r="19" ht="90" spans="1:9">
       <c r="A19" s="4">
         <v>10016</v>
       </c>
@@ -1977,7 +1983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="104" spans="1:9">
+    <row r="20" ht="90" spans="1:9">
       <c r="A20" s="4">
         <v>10017</v>
       </c>
@@ -2006,7 +2012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="104" spans="1:9">
+    <row r="21" ht="90" spans="1:9">
       <c r="A21" s="4">
         <v>10018</v>
       </c>
@@ -2035,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="172" spans="1:9">
+    <row r="22" ht="150" spans="1:9">
       <c r="A22" s="4">
         <v>10019</v>
       </c>
@@ -2064,7 +2070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="138" spans="1:9">
+    <row r="23" ht="120" spans="1:9">
       <c r="A23" s="4">
         <v>10020</v>
       </c>
@@ -2093,7 +2099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="138" spans="1:9">
+    <row r="24" ht="120" spans="1:9">
       <c r="A24" s="4">
         <v>10021</v>
       </c>
@@ -2122,7 +2128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="69" spans="1:9">
+    <row r="25" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A25" s="5">
         <v>10022</v>
       </c>
@@ -2141,17 +2147,17 @@
       <c r="F25" s="5">
         <v>0</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H25" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="138" spans="1:9">
+      <c r="H25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="120" spans="1:9">
       <c r="A26" s="4">
         <v>10023</v>
       </c>
@@ -2180,7 +2186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="241" spans="1:9">
+    <row r="27" ht="210" spans="1:9">
       <c r="A27" s="4">
         <v>10024</v>
       </c>
@@ -2209,7 +2215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="69" spans="1:9">
+    <row r="28" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A28" s="5">
         <v>10025</v>
       </c>
@@ -2228,17 +2234,17 @@
       <c r="F28" s="5">
         <v>0</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H28" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="69" spans="1:9">
+      <c r="H28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A29" s="5">
         <v>10026</v>
       </c>
@@ -2257,17 +2263,17 @@
       <c r="F29" s="5">
         <v>0</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H29" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="69" spans="1:9">
+      <c r="H29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A30" s="5">
         <v>10027</v>
       </c>
@@ -2286,17 +2292,17 @@
       <c r="F30" s="5">
         <v>0</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H30" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="69" spans="1:9">
+      <c r="H30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="60" spans="1:9">
       <c r="A31" s="5">
         <v>10028</v>
       </c>
@@ -2315,17 +2321,17 @@
       <c r="F31" s="5">
         <v>0</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="8" t="b">
+      <c r="H31" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I31" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="104" spans="1:9">
+    <row r="32" ht="90" spans="1:9">
       <c r="A32" s="4">
         <v>10029</v>
       </c>
@@ -2354,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="138" spans="1:9">
+    <row r="33" ht="120" spans="1:9">
       <c r="A33" s="4">
         <v>10030</v>
       </c>
@@ -2383,7 +2389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="138" spans="1:9">
+    <row r="34" ht="120" spans="1:9">
       <c r="A34" s="4">
         <v>10031</v>
       </c>
@@ -2412,7 +2418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="69" spans="1:9">
+    <row r="35" ht="60" spans="1:9">
       <c r="A35" s="4">
         <v>10032</v>
       </c>
@@ -2441,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="69" spans="1:9">
+    <row r="36" ht="60" spans="1:9">
       <c r="A36" s="4">
         <v>10033</v>
       </c>
@@ -2470,7 +2476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="69" spans="1:9">
+    <row r="37" ht="60" spans="1:9">
       <c r="A37" s="4">
         <v>10034</v>
       </c>
@@ -2499,7 +2505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" ht="69" spans="1:9">
+    <row r="38" ht="60" spans="1:9">
       <c r="A38" s="4">
         <v>10035</v>
       </c>
@@ -2528,7 +2534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="138" spans="1:9">
+    <row r="39" ht="120" spans="1:9">
       <c r="A39" s="4">
         <v>10036</v>
       </c>
@@ -2557,7 +2563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" ht="172" spans="1:9">
+    <row r="40" ht="150" spans="1:9">
       <c r="A40" s="4">
         <v>10037</v>
       </c>
@@ -2586,14 +2592,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="172" spans="1:9">
+    <row r="41" ht="150" spans="1:9">
       <c r="A41" s="4">
         <v>10038</v>
       </c>
       <c r="B41" s="4">
         <v>0</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="8">
         <v>10550</v>
       </c>
       <c r="D41" s="4" t="b">
@@ -2615,7 +2621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="207" spans="1:9">
+    <row r="42" ht="180" spans="1:9">
       <c r="A42" s="4">
         <v>10039</v>
       </c>
@@ -2644,17 +2650,63 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="F44" s="4"/>
+    <row r="43" ht="240" spans="1:9">
+      <c r="A43" s="4">
+        <v>10040</v>
+      </c>
+      <c r="B43" s="4">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4">
+        <v>10950</v>
+      </c>
+      <c r="D43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4">
+        <v>10019</v>
+      </c>
+      <c r="F43" s="4">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="240" spans="1:9">
+      <c r="A44" s="4">
+        <v>10041</v>
+      </c>
+      <c r="B44" s="4">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4">
+        <v>10950</v>
+      </c>
+      <c r="D44" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="4">
+        <v>10019</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H44" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="4"/>

--- a/Excel/RoleDialogDatas.xlsx
+++ b/Excel/RoleDialogDatas.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
   <si>
     <t>int</t>
   </si>
@@ -185,10 +185,10 @@
     <t>鲍勃未喝牛奶难入眠，出门遭遇了怪物</t>
   </si>
   <si>
-    <t>迈克再次进入“梦世界”</t>
-  </si>
-  <si>
-    <t>迈克艰难逃脱后</t>
+    <t>迈克再次进入“梦世界”的自言自语</t>
+  </si>
+  <si>
+    <t>迈克大杀四方后发现自己击杀了Bob</t>
   </si>
   <si>
     <t>迈克听到有人敲门</t>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>一些上帝引导,这是第二天让玩家和Bob在客厅里喝牛奶，不要让玩家到院子去的引导</t>
+  </si>
+  <si>
+    <t>玩家击杀战斗场景所有敌人后，触发鲍勃的惊恐声音</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="60" spans="1:9">
+    <row r="35" ht="90" spans="1:9">
       <c r="A35" s="4">
         <v>10032</v>
       </c>
@@ -2432,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="4">
-        <v>10031</v>
+        <v>-1</v>
       </c>
       <c r="F35" s="4">
         <v>1</v>
@@ -2444,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="60" spans="1:9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="90" spans="1:9">
       <c r="A36" s="4">
         <v>10033</v>
       </c>
@@ -2473,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="60" spans="1:9">
@@ -2548,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="4">
-        <v>10035</v>
+        <v>-1</v>
       </c>
       <c r="F39" s="4">
         <v>1</v>
@@ -2560,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" ht="150" spans="1:9">
@@ -2708,16 +2711,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="4"/>
-    </row>
-    <row r="46" spans="1:1">
+    <row r="45" ht="150" spans="1:9">
+      <c r="A45" s="4">
+        <v>10042</v>
+      </c>
+      <c r="B45" s="4">
+        <v>0</v>
+      </c>
+      <c r="C45" s="4">
+        <v>2501</v>
+      </c>
+      <c r="D45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4">
+        <v>-1</v>
+      </c>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H45" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="4"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:9">
       <c r="A47" s="4"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:9">
       <c r="A48" s="4"/>
     </row>
     <row r="49" spans="1:1">

--- a/Excel/RoleDialogDatas.xlsx
+++ b/Excel/RoleDialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12780"/>
+    <workbookView windowHeight="15060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1423,16 +1423,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="9.22222222222222" defaultRowHeight="30.6"/>
+  <sheetFormatPr defaultColWidth="9.22115384615385" defaultRowHeight="34.4"/>
   <cols>
-    <col min="1" max="1" width="19.5555555555556" style="2" customWidth="1"/>
-    <col min="2" max="2" width="58.9814814814815" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.4444444444444" style="2" customWidth="1"/>
-    <col min="4" max="4" width="39.5555555555556" style="2" customWidth="1"/>
-    <col min="5" max="5" width="37.7777777777778" style="2" customWidth="1"/>
+    <col min="1" max="1" width="19.5576923076923" style="2" customWidth="1"/>
+    <col min="2" max="2" width="58.9807692307692" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.4423076923077" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.5576923076923" style="2" customWidth="1"/>
+    <col min="5" max="5" width="37.7788461538462" style="2" customWidth="1"/>
     <col min="6" max="6" width="35.25" style="2" customWidth="1"/>
-    <col min="7" max="9" width="27.5555555555556" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.22222222222222" style="2"/>
+    <col min="7" max="9" width="27.5576923076923" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.22115384615385" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1696,7 +1696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="10" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A10" s="5">
         <v>10007</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="11" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A11" s="5">
         <v>10008</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="12" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A12" s="5">
         <v>10009</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="13" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A13" s="5">
         <v>10010</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="14" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A14" s="5">
         <v>10011</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="60" spans="1:9">
+    <row r="15" ht="69" spans="1:9">
       <c r="A15" s="4">
         <v>10012</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="90" spans="1:9">
+    <row r="16" s="1" customFormat="1" ht="104" spans="1:9">
       <c r="A16" s="5">
         <v>10013</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="90" spans="1:9">
+    <row r="17" ht="104" spans="1:9">
       <c r="A17" s="4">
         <v>10014</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="90" spans="1:9">
+    <row r="18" ht="104" spans="1:9">
       <c r="A18" s="4">
         <v>10015</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="90" spans="1:9">
+    <row r="19" ht="104" spans="1:9">
       <c r="A19" s="4">
         <v>10016</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="90" spans="1:9">
+    <row r="20" ht="104" spans="1:9">
       <c r="A20" s="4">
         <v>10017</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="90" spans="1:9">
+    <row r="21" ht="104" spans="1:9">
       <c r="A21" s="4">
         <v>10018</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="150" spans="1:9">
+    <row r="22" ht="172" spans="1:9">
       <c r="A22" s="4">
         <v>10019</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="120" spans="1:9">
+    <row r="23" ht="138" spans="1:9">
       <c r="A23" s="4">
         <v>10020</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="120" spans="1:9">
+    <row r="24" ht="138" spans="1:9">
       <c r="A24" s="4">
         <v>10021</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="25" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A25" s="5">
         <v>10022</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="120" spans="1:9">
+    <row r="26" ht="138" spans="1:9">
       <c r="A26" s="4">
         <v>10023</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="210" spans="1:9">
+    <row r="27" ht="241" spans="1:9">
       <c r="A27" s="4">
         <v>10024</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="28" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A28" s="5">
         <v>10025</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="29" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A29" s="5">
         <v>10026</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="30" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A30" s="5">
         <v>10027</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="60" spans="1:9">
+    <row r="31" s="1" customFormat="1" ht="69" spans="1:9">
       <c r="A31" s="5">
         <v>10028</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="90" spans="1:9">
+    <row r="32" ht="104" spans="1:9">
       <c r="A32" s="4">
         <v>10029</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="120" spans="1:9">
+    <row r="33" ht="138" spans="1:9">
       <c r="A33" s="4">
         <v>10030</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="120" spans="1:9">
+    <row r="34" ht="138" spans="1:9">
       <c r="A34" s="4">
         <v>10031</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="90" spans="1:9">
+    <row r="35" ht="104" spans="1:9">
       <c r="A35" s="4">
         <v>10032</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="90" spans="1:9">
+    <row r="36" ht="104" spans="1:9">
       <c r="A36" s="4">
         <v>10033</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="60" spans="1:9">
+    <row r="37" ht="69" spans="1:9">
       <c r="A37" s="4">
         <v>10034</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" ht="60" spans="1:9">
+    <row r="38" ht="69" spans="1:9">
       <c r="A38" s="4">
         <v>10035</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="120" spans="1:9">
+    <row r="39" ht="138" spans="1:9">
       <c r="A39" s="4">
         <v>10036</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" ht="150" spans="1:9">
+    <row r="40" ht="172" spans="1:9">
       <c r="A40" s="4">
         <v>10037</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="150" spans="1:9">
+    <row r="41" ht="172" spans="1:9">
       <c r="A41" s="4">
         <v>10038</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" ht="180" spans="1:9">
+    <row r="42" ht="207" spans="1:9">
       <c r="A42" s="4">
         <v>10039</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="240" spans="1:9">
+    <row r="43" ht="276" spans="1:9">
       <c r="A43" s="4">
         <v>10040</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="240" spans="1:9">
+    <row r="44" ht="276" spans="1:9">
       <c r="A44" s="4">
         <v>10041</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" ht="150" spans="1:9">
+    <row r="45" ht="172" spans="1:9">
       <c r="A45" s="4">
         <v>10042</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="C45" s="4">
-        <v>2501</v>
+        <v>2551</v>
       </c>
       <c r="D45" s="4" t="b">
         <v>0</v>

--- a/Excel/RoleDialogDatas.xlsx
+++ b/Excel/RoleDialogDatas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15060"/>
+    <workbookView windowHeight="15000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,19 +41,19 @@
     <t>对话数据的id</t>
   </si>
   <si>
-    <t>对话主体的类型：0代表主角，1代表Mom，2代表Bob，3代表God，4代表TV，5代表相框，6代表桌子，7代表猫，8代表狗，9代表炸鸡店，10代表糖果店，11代表花店，12代表路人甲，13代表路人乙，14代表路人丙，15代表路人丁，16代表David‘Mom</t>
+    <t>对话主体的类型：0代表主角,1代表Mom,2代表Bob,3代表God,4代表TV,5代表相框,6代表桌子,7代表猫,8代表狗,9代表炸鸡店,10代表糖果店,11代表花店,12代表路人甲,13代表路人乙,14代表路人丙,15代表路人丁,16代表David‘Mom</t>
   </si>
   <si>
     <t>对话数据的开始id</t>
   </si>
   <si>
-    <t>对话是否可以重复触发，true表示可以，如电视等，false表示不可以，即触发一次之后再也不会触发第二次</t>
-  </si>
-  <si>
-    <t>这个对话是否需要前置数据才能解锁，如果没有，填-1，有，填对应的id</t>
-  </si>
-  <si>
-    <t>是否是剧情对话,1表示是剧情对话，由剧情系统驱动，0表示有玩家交互驱动</t>
+    <t>对话是否可以重复触发,true表示可以,如电视等,false表示不可以,即触发一次之后再也不会触发第二次</t>
+  </si>
+  <si>
+    <t>这个对话是否需要前置数据才能解锁,如果没有,填-1,有,填对应的id</t>
+  </si>
+  <si>
+    <t>是否是剧情对话,1表示是剧情对话,由剧情系统驱动,0表示有玩家交互驱动</t>
   </si>
   <si>
     <t>为对话添加的描述</t>
@@ -146,22 +146,22 @@
     <t>迈克重回现实世界的自白</t>
   </si>
   <si>
-    <t>迈克在首次离开梦世界后，与鲍勃的分享梦世界的对话</t>
-  </si>
-  <si>
-    <t>迈克尝试在白天喝牛奶，遭到妈妈的制止</t>
-  </si>
-  <si>
-    <t>在被制止后，两人商量给猫来一瓶牛奶试试</t>
+    <t>迈克在首次离开梦世界后,与鲍勃的分享梦世界的对话</t>
+  </si>
+  <si>
+    <t>迈克尝试在白天喝牛奶,遭到妈妈的制止</t>
+  </si>
+  <si>
+    <t>在被制止后,两人商量给猫来一瓶牛奶试试</t>
   </si>
   <si>
     <t>猫喝完牛奶后呼呼大睡</t>
   </si>
   <si>
-    <t>在猫睡着后，两人拿走了猫的铃铛</t>
-  </si>
-  <si>
-    <t>充满疑问的迈克闻讯了路人甲关于牛奶的问题，但只能得到摸棱两可的回答</t>
+    <t>在猫睡着后,两人拿走了猫的铃铛</t>
+  </si>
+  <si>
+    <t>充满疑问的迈克闻讯了路人甲关于牛奶的问题,但只能得到摸棱两可的回答</t>
   </si>
   <si>
     <t>交互对话：路人乙</t>
@@ -182,7 +182,7 @@
     <t>鲍勃家视角：鲍勃妈妈提醒鲍勃喝牛奶</t>
   </si>
   <si>
-    <t>鲍勃未喝牛奶难入眠，出门遭遇了怪物</t>
+    <t>鲍勃未喝牛奶难入眠,出门遭遇了怪物</t>
   </si>
   <si>
     <t>迈克再次进入“梦世界”的自言自语</t>
@@ -197,7 +197,7 @@
     <t>门外的鲍勃在求助</t>
   </si>
   <si>
-    <t>迈克兽性大发，吃掉了朋友，游戏结束</t>
+    <t>迈克兽性大发,吃掉了朋友,游戏结束</t>
   </si>
   <si>
     <t>一些上帝引导,这是玩家不触发bob敲门不让他出门的引导</t>
@@ -209,13 +209,13 @@
     <t>一些上帝引导,这是第二天让玩家和Bob在院子中进行探索的引导</t>
   </si>
   <si>
-    <t>一些上帝引导,这是第二天让玩家和Bob在客厅里喝牛奶，不要让玩家到卧室去的引导</t>
-  </si>
-  <si>
-    <t>一些上帝引导,这是第二天让玩家和Bob在客厅里喝牛奶，不要让玩家到院子去的引导</t>
-  </si>
-  <si>
-    <t>玩家击杀战斗场景所有敌人后，触发鲍勃的惊恐声音</t>
+    <t>一些上帝引导,这是第二天让玩家和Bob在客厅里喝牛奶,不要让玩家到卧室去的引导</t>
+  </si>
+  <si>
+    <t>一些上帝引导,这是第二天让玩家和Bob在客厅里喝牛奶,不要让玩家到院子去的引导</t>
+  </si>
+  <si>
+    <t>玩家击杀战斗场景所有敌人后,触发鲍勃的惊恐声音</t>
   </si>
 </sst>
 </file>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="138" spans="1:9">
+    <row r="26" ht="104" spans="1:9">
       <c r="A26" s="4">
         <v>10023</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="138" spans="1:9">
+    <row r="39" ht="104" spans="1:9">
       <c r="A39" s="4">
         <v>10036</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="276" spans="1:9">
+    <row r="43" ht="241" spans="1:9">
       <c r="A43" s="4">
         <v>10040</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="276" spans="1:9">
+    <row r="44" ht="241" spans="1:9">
       <c r="A44" s="4">
         <v>10041</v>
       </c>
